--- a/sitepreview/trust/StructureDefinition-HCert.xlsx
+++ b/sitepreview/trust/StructureDefinition-HCert.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-05-19T11:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -308,14 +308,14 @@
     <t>HCert.-6</t>
   </si>
   <si>
-    <t xml:space="preserve">http://smart.who.int/trust-phw/StructureDefinition/DVC
+    <t xml:space="preserve">http://smart.who.int/trust-phw/StructureDefinition/DVCMin
 </t>
   </si>
   <si>
-    <t>DVC</t>
-  </si>
-  <si>
-    <t>Digital Vaccination Certificate (Proposed)</t>
+    <t>DVCMin</t>
+  </si>
+  <si>
+    <t>Minimal Digital Vaccination Certificate Payload (Proposed)</t>
   </si>
 </sst>
 </file>
@@ -993,7 +993,7 @@
         <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>73</v>
@@ -1068,7 +1068,7 @@
         <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
@@ -1096,7 +1096,7 @@
         <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1171,7 +1171,7 @@
         <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1199,7 +1199,7 @@
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1274,7 +1274,7 @@
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1302,7 +1302,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1377,7 +1377,7 @@
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
